--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED10.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED10.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:53+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>273W</t>
+          <t>189W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L6"/>
+  <dimension ref="B2:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -1700,7 +1700,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-2-0013</t>
+          <t>SIM_XA_FIXED-3-0066</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1714,11 +1714,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>51W</t>
+          <t>143W</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>第2年</t>
+          <t>第3年</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1748,117 +1748,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>第2年4季</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SIM_XA_FIXED-3-0017</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>本地</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>165W</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>已交</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>第3年</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5季</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>3季</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>第4年1季</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>SIM_XA_FIXED-4-0081</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>本地</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>147W</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>已交</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>第4年</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5季</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>3季</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>第5年1季</t>
+          <t>第4年3季</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G60"/>
+  <dimension ref="B2:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2196,10 +2086,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="E14" t="n">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2225,7 +2115,7 @@
         <v>-14</v>
       </c>
       <c r="E15" t="n">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2244,14 +2134,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-24</v>
+        <v>-14</v>
       </c>
       <c r="E16" t="n">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2260,7 +2150,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2270,23 +2160,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="E17" t="n">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>第2年2季</t>
+          <t>第2年3季</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-b5c45c6a9e", "line_id": "L-30f5df7204", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2303,11 +2193,11 @@
         <v>-14</v>
       </c>
       <c r="E18" t="n">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>第2年2季</t>
+          <t>第2年4季</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2322,23 +2212,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="E19" t="n">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>第2年3季</t>
+          <t>第2年4季</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>maintenance_expense | {"line_id": "L-30f5df7204"}</t>
         </is>
       </c>
     </row>
@@ -2348,14 +2238,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2364,7 +2254,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 40.0, "order_id": "SIM_XA_FIXED-2-0013", "receivable_term_quarters": 2, "revenue_wan": 51.0}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-30f5df7204", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2374,14 +2264,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>378</v>
+        <v>417</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2280,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-30f5df7204", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2400,23 +2290,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-16</v>
+        <v>-4</v>
       </c>
       <c r="E22" t="n">
-        <v>362</v>
+        <v>413</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-4e7413fbd3", "line_id": "L-30f5df7204", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
         </is>
       </c>
     </row>
@@ -2433,11 +2323,11 @@
         <v>-14</v>
       </c>
       <c r="E23" t="n">
-        <v>348</v>
+        <v>399</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2452,23 +2342,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E24" t="n">
-        <v>333</v>
+        <v>385</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-30f5df7204"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2478,23 +2368,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E25" t="n">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-30f5df7204", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2504,23 +2394,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E26" t="n">
-        <v>333</v>
+        <v>357</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-30f5df7204", "asset_type": "production_line"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2530,23 +2420,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-8</v>
+        <v>-15</v>
       </c>
       <c r="E27" t="n">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>maintenance_expense | {"line_id": "L-30f5df7204"}</t>
         </is>
       </c>
     </row>
@@ -2556,23 +2446,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>311</v>
+        <v>342</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-30f5df7204", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2582,23 +2472,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-8de5801165"}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-30f5df7204", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2608,23 +2498,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-14</v>
+        <v>-48</v>
       </c>
       <c r="E30" t="n">
-        <v>348</v>
+        <v>294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
         </is>
       </c>
     </row>
@@ -2634,23 +2524,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="E31" t="n">
-        <v>324</v>
+        <v>262</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-925500f08c", "line_id": "L-30f5df7204", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2660,23 +2550,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-16</v>
+        <v>-4</v>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>258</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-4f23ce1ad3", "line_id": "L-30f5df7204", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2693,11 +2583,11 @@
         <v>-14</v>
       </c>
       <c r="E33" t="n">
-        <v>294</v>
+        <v>244</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2719,11 +2609,11 @@
         <v>-14</v>
       </c>
       <c r="E34" t="n">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2738,23 +2628,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-30f5df7204"}</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-3-0066", "receivable_term_quarters": 2, "revenue_wan": 143.0}</t>
         </is>
       </c>
     </row>
@@ -2764,23 +2654,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="E36" t="n">
-        <v>265</v>
+        <v>182</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-30f5df7204", "asset_type": "factory"}</t>
+          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
         </is>
       </c>
     </row>
@@ -2790,23 +2680,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="E37" t="n">
-        <v>265</v>
+        <v>150</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-30f5df7204", "asset_type": "production_line"}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-ed9a74823f", "line_id": "L-30f5df7204", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2816,23 +2706,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E38" t="n">
-        <v>265</v>
+        <v>136</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-3-0017", "receivable_term_quarters": 3, "revenue_wan": 165.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2842,23 +2732,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-48</v>
+        <v>-14</v>
       </c>
       <c r="E39" t="n">
-        <v>217</v>
+        <v>122</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2868,23 +2758,23 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-32</v>
+        <v>143</v>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>265</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-925500f08c", "line_id": "L-30f5df7204", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
+          <t>receivable_collected | {"receivable_id": "AR-589373bfc2"}</t>
         </is>
       </c>
     </row>
@@ -2894,23 +2784,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-8</v>
+        <v>-15</v>
       </c>
       <c r="E41" t="n">
-        <v>177</v>
+        <v>250</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>maintenance_expense | {"line_id": "L-30f5df7204"}</t>
         </is>
       </c>
     </row>
@@ -2920,23 +2810,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-30f5df7204", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2946,23 +2836,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>149</v>
+        <v>250</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-30f5df7204", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2972,23 +2862,23 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="E44" t="n">
-        <v>135</v>
+        <v>246</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2998,23 +2888,23 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>165</v>
+        <v>-14</v>
       </c>
       <c r="E45" t="n">
-        <v>300</v>
+        <v>232</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-e705c46c30"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -3031,11 +2921,11 @@
         <v>-14</v>
       </c>
       <c r="E46" t="n">
-        <v>286</v>
+        <v>218</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3050,23 +2940,23 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E47" t="n">
-        <v>271</v>
+        <v>204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年3季</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-30f5df7204"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -3076,23 +2966,23 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E48" t="n">
-        <v>271</v>
+        <v>189</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-30f5df7204", "asset_type": "factory"}</t>
+          <t>maintenance_expense | {"line_id": "L-30f5df7204"}</t>
         </is>
       </c>
     </row>
@@ -3109,16 +2999,16 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>271</v>
+        <v>189</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-30f5df7204", "asset_type": "production_line"}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-30f5df7204", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -3128,281 +3018,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D50" t="n">
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>271</v>
+        <v>189</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
-        <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-4-0081", "receivable_term_quarters": 3, "revenue_wan": 147.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="n">
-        <v>48</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Emergency_Buy_Material</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>-48</v>
-      </c>
-      <c r="E51" t="n">
-        <v>223</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>第5年1季</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" t="n">
-        <v>49</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Product_Produce</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>-32</v>
-      </c>
-      <c r="E52" t="n">
-        <v>191</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>第5年1季</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-115fa2b5d2", "line_id": "L-30f5df7204", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" t="n">
-        <v>50</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Pay_AD</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>-8</v>
-      </c>
-      <c r="E53" t="n">
-        <v>183</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>第5年1季</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" t="n">
-        <v>51</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Pay_Overhaul</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E54" t="n">
-        <v>169</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>第5年1季</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>management_fee_expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" t="n">
-        <v>52</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Pay_Overhaul</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E55" t="n">
-        <v>155</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>第5年2季</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>management_fee_expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" t="n">
-        <v>53</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Pay_Overhaul</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E56" t="n">
-        <v>141</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>第5年3季</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>management_fee_expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" t="n">
-        <v>54</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Update_Receivable</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>147</v>
-      </c>
-      <c r="E57" t="n">
-        <v>288</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>第5年3季</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>receivable_collected | {"receivable_id": "AR-8399fbeb59"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" t="n">
-        <v>55</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Pay_Maintenance</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>-15</v>
-      </c>
-      <c r="E58" t="n">
-        <v>273</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>maintenance_expense | {"line_id": "L-30f5df7204"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" t="n">
-        <v>56</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" t="n">
-        <v>273</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-30f5df7204", "asset_type": "factory"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" t="n">
-        <v>57</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="n">
-        <v>273</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
         <is>
           <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-30f5df7204", "asset_type": "production_line"}</t>
         </is>
@@ -3509,16 +3139,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -3734,16 +3364,16 @@
         <v>71</v>
       </c>
       <c r="E13" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F13" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G13" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H13" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -3796,16 +3426,16 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="H16" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3821,7 +3451,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -3830,7 +3460,7 @@
         <v>80</v>
       </c>
       <c r="H17" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3846,16 +3476,16 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="H18" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3871,16 +3501,16 @@
         <v>71</v>
       </c>
       <c r="E19" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F19" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G19" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H19" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20">
@@ -3896,16 +3526,16 @@
         <v>-71</v>
       </c>
       <c r="E20" t="n">
-        <v>-68</v>
+        <v>-75</v>
       </c>
       <c r="F20" t="n">
-        <v>-79</v>
+        <v>-75</v>
       </c>
       <c r="G20" t="n">
-        <v>6</v>
+        <v>-12</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>-61</v>
       </c>
     </row>
     <row r="21">
@@ -3946,16 +3576,16 @@
         <v>-86.2</v>
       </c>
       <c r="E22" t="n">
-        <v>-83.2</v>
+        <v>-90.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-94.2</v>
+        <v>-90.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-9.199999999999999</v>
+        <v>-27.2</v>
       </c>
       <c r="H22" t="n">
-        <v>-13.2</v>
+        <v>-76.2</v>
       </c>
     </row>
     <row r="23">
@@ -3996,16 +3626,16 @@
         <v>-86.2</v>
       </c>
       <c r="E24" t="n">
-        <v>-83.2</v>
+        <v>-90.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-94.2</v>
+        <v>-90.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-9.199999999999999</v>
+        <v>-27.2</v>
       </c>
       <c r="H24" t="n">
-        <v>-13.2</v>
+        <v>-76.2</v>
       </c>
     </row>
     <row r="25">
@@ -4046,16 +3676,16 @@
         <v>-86.2</v>
       </c>
       <c r="E26" t="n">
-        <v>-83.2</v>
+        <v>-90.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-94.2</v>
+        <v>-90.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-9.199999999999999</v>
+        <v>-27.2</v>
       </c>
       <c r="H26" t="n">
-        <v>-13.2</v>
+        <v>-76.2</v>
       </c>
     </row>
     <row r="28">
@@ -4145,16 +3775,16 @@
         <v>492</v>
       </c>
       <c r="E30" t="n">
-        <v>333</v>
+        <v>417</v>
       </c>
       <c r="F30" t="n">
-        <v>265</v>
+        <v>342</v>
       </c>
       <c r="G30" t="n">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="H30" t="n">
-        <v>273</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31">
@@ -4170,7 +3800,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -4195,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -4223,7 +3853,7 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>80</v>
@@ -4270,16 +3900,16 @@
         <v>492</v>
       </c>
       <c r="E35" t="n">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="F35" t="n">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G35" t="n">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="H35" t="n">
-        <v>353</v>
+        <v>269</v>
       </c>
     </row>
     <row r="36">
@@ -4395,16 +4025,16 @@
         <v>588.8</v>
       </c>
       <c r="E40" t="n">
-        <v>505.6</v>
+        <v>498.6</v>
       </c>
       <c r="F40" t="n">
-        <v>411.4</v>
+        <v>408.4</v>
       </c>
       <c r="G40" t="n">
-        <v>402.2</v>
+        <v>381.2</v>
       </c>
       <c r="H40" t="n">
-        <v>389</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41">
@@ -4570,16 +4200,16 @@
         <v>-4.263256414560601e-14</v>
       </c>
       <c r="E47" t="n">
-        <v>-86.20000000000009</v>
+        <v>-86.20000000000003</v>
       </c>
       <c r="F47" t="n">
-        <v>-169.4000000000001</v>
+        <v>-176.4</v>
       </c>
       <c r="G47" t="n">
-        <v>-263.6000000000001</v>
+        <v>-266.6</v>
       </c>
       <c r="H47" t="n">
-        <v>-272.8000000000001</v>
+        <v>-293.8</v>
       </c>
     </row>
     <row r="48">
@@ -4595,16 +4225,16 @@
         <v>-86.2</v>
       </c>
       <c r="E48" t="n">
-        <v>-83.2</v>
+        <v>-90.2</v>
       </c>
       <c r="F48" t="n">
-        <v>-94.2</v>
+        <v>-90.2</v>
       </c>
       <c r="G48" t="n">
-        <v>-9.199999999999999</v>
+        <v>-27.2</v>
       </c>
       <c r="H48" t="n">
-        <v>-13.2</v>
+        <v>-76.2</v>
       </c>
     </row>
     <row r="49">
@@ -4620,16 +4250,16 @@
         <v>588.8</v>
       </c>
       <c r="E49" t="n">
-        <v>505.5999999999999</v>
+        <v>498.6</v>
       </c>
       <c r="F49" t="n">
-        <v>411.3999999999999</v>
+        <v>408.4</v>
       </c>
       <c r="G49" t="n">
-        <v>402.1999999999999</v>
+        <v>381.2</v>
       </c>
       <c r="H49" t="n">
-        <v>388.9999999999999</v>
+        <v>305</v>
       </c>
     </row>
     <row r="50">
@@ -4645,16 +4275,16 @@
         <v>588.8</v>
       </c>
       <c r="E50" t="n">
-        <v>505.5999999999999</v>
+        <v>498.6</v>
       </c>
       <c r="F50" t="n">
-        <v>411.3999999999999</v>
+        <v>408.4</v>
       </c>
       <c r="G50" t="n">
-        <v>402.1999999999999</v>
+        <v>381.2</v>
       </c>
       <c r="H50" t="n">
-        <v>388.9999999999999</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -4725,7 +4355,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4874,7 +4504,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -5023,7 +4653,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -5172,7 +4802,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -5321,7 +4951,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
